--- a/master/所需做的实验.xlsx
+++ b/master/所需做的实验.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
   <si>
     <t xml:space="preserve">Algorithm</t>
   </si>
@@ -43,6 +43,7 @@
         <color rgb="FF000000"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">定点</t>
     </r>
@@ -77,6 +78,7 @@
         <color rgb="FF000000"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">圆</t>
     </r>
@@ -111,6 +113,7 @@
         <color rgb="FF000000"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">八字</t>
     </r>
@@ -130,6 +133,9 @@
     <t xml:space="preserve">FNTSMC</t>
   </si>
   <si>
+    <t xml:space="preserve">OK</t>
+  </si>
+  <si>
     <t xml:space="preserve">FNTSMC+RL</t>
   </si>
   <si>
@@ -143,9 +149,6 @@
   </si>
   <si>
     <t xml:space="preserve">PX4-PID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OK</t>
   </si>
   <si>
     <t xml:space="preserve">FT-PD [ref]</t>
@@ -198,6 +201,7 @@
       <color rgb="FF000000"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -290,7 +294,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -380,7 +384,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="21"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16.74"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13.89"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="5" style="1" width="9"/>
   </cols>
@@ -404,45 +408,57 @@
         <v>4</v>
       </c>
       <c r="B2" s="4"/>
-      <c r="C2" s="5"/>
+      <c r="C2" s="5" t="s">
+        <v>5</v>
+      </c>
       <c r="D2" s="5"/>
     </row>
     <row r="3" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
+      <c r="C3" s="5" t="s">
+        <v>5</v>
+      </c>
       <c r="D3" s="5"/>
     </row>
     <row r="4" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
+      <c r="C4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="5"/>
+        <v>10</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>5</v>
+      </c>
       <c r="C6" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="5"/>
+        <v>5</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
@@ -458,9 +474,11 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="5"/>
+        <v>5</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
